--- a/Тест2/281.xlsx
+++ b/Тест2/281.xlsx
@@ -168,19 +168,19 @@
     <t xml:space="preserve">Yuza kichik bo'lsa surtma qanday olinadi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Narsa surtilmay, o'tkazib yuboriladi</t>
+    <t xml:space="preserve">Surtilmay, o'tkazib yuboriladi va yozilmaydi</t>
   </si>
   <si>
     <t xml:space="preserve">Butun yuza surtilib, yo'llanma xatda qayd etiladi</t>
   </si>
   <si>
-    <t xml:space="preserve">Maydon taxminiy belgilanib, yozilmaydi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boshqa buyumdan olinib, almashtiriladi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chetlari surtilib, natija yoziladi</t>
+    <t xml:space="preserve">Maydon taxminiy belgilanib, qayd etilmaydi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boshqa buyumdan olinib, almashtirib qo'yiladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chetlari surtilib, natija yoziladi va tugaydi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Butun yuza surtilib, yo'llanma xatda qayd etiladi. Yuza kichik bo'lsa butun yuza surtiladi va bu yo'llanma xatda qayd etiladi. Manba: Mavzu materiali (281.docx).</t>
